--- a/Accessory/preset_matrix.xlsx
+++ b/Accessory/preset_matrix.xlsx
@@ -659,12 +659,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>**native（暂留，§13.10.1）**</t>
+          <t>6（显式 -speed 6，与 native 逐字节相同，零回归）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/Accessory/preset_matrix.xlsx
+++ b/Accessory/preset_matrix.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,77 +417,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="11.4" customWidth="1" min="1" max="1"/>
+    <col width="9.6" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="7.9" customWidth="1" min="4" max="4"/>
+    <col width="25.3" customWidth="1" min="5" max="5"/>
+    <col width="9.9" customWidth="1" min="6" max="6"/>
+    <col width="9.4" customWidth="1" min="7" max="7"/>
+    <col width="9.1" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7.1" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13.9" customWidth="1" min="12" max="12"/>
+    <col width="9.1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>libx264</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>preset</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ultrafast</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>veryfast</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>fast</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>**medium**</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>slower</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>veryslow</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>veryslow</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>编码器</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>控制参数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>级别范围</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>速度/质量倾向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>preview</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>near-lossless</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lossless</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>libx265</t>
+          <t>libx264</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,49 +515,64 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>ultrafast/superfast/veryfast/faster/fast/medium/slow/slower/veryslow/placebo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>速度越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ultrafast</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>veryfast</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>veryfast</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>**faster**</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>**medium**</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>slower</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>**slower**</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>**slower**</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>veryslow</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>veryslow</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>libsvtav1</t>
+          <t>libx265</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,92 +582,122 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>ultrafast/superfast/veryfast/faster/fast/medium/slow/slower/veryslow/placebo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>速度越慢，质量越高</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>**8**</t>
+          <t>veryfast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>veryfast</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>**faster**</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>**medium**</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>slower</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>**slower**</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>**slower**</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>libvpx-vp9</t>
+          <t>libsvtav1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cpu-used</t>
+          <t>preset</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>数值越小越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>**8**</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>**恒等值（待定，§13.4）**</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -639,50 +706,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>librav1e</t>
+          <t>libvpx-vp9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>cpu-used</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>数值越小越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6（显式 -speed 6，与 native 逐字节相同，零回归）</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>**恒等值（待定，§13.4）**</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -691,50 +773,65 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>libaom-av1</t>
+          <t>librav1e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cpu-used</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0,10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>数值越小越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>**恒等值（待定，§13.4）**</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6（显式 -speed 6，与 native 逐字节相同，零回归）</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -743,59 +840,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>h264_nvenc</t>
+          <t>libaom-av1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>preset</t>
+          <t>cpu-used</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>数值越小越慢，质量越高</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>**p4**</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>**恒等值（待定，§13.4）**</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hevc_nvenc</t>
+          <t>h264_nvenc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -805,40 +917,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>p1,p7</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>p值越大越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>**p4**</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -847,50 +974,132 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>hevc_nvenc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>preset</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>p1,p7</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>p值越大越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>**p4**</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>av1_nvenc</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>preset</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>p1,p7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>p值越大越慢，质量越高</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>**p4**</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>p7</t>
         </is>

--- a/Accessory/preset_matrix.xlsx
+++ b/Accessory/preset_matrix.xlsx
@@ -420,8 +420,8 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.4" customWidth="1" min="1" max="1"/>
-    <col width="9.6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="78" customWidth="1" min="3" max="3"/>
     <col width="7.9" customWidth="1" min="4" max="4"/>
     <col width="25.3" customWidth="1" min="5" max="5"/>
@@ -438,7 +438,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>编码器</t>
+          <t>Codec / 编码器</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>**balanced**</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>**恒等值（待定，§13.4）**</t>
+          <t>**恒等值（待定，§13.4，已拍板=2）**</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/Accessory/preset_matrix.xlsx
+++ b/Accessory/preset_matrix.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>veryfast</t>
+          <t>ultrafast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>-8,8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -746,22 +746,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>**恒等值（待定，§13.4，已拍板=2）**</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0,10</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>native（0）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>auto（4/5/6/8）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>**恒等值（待定，§13.4）**</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>p1,p7</t>
+          <t>p1~p7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>p1,p7</t>
+          <t>p1~p7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>p1,p7</t>
+          <t>p1~p7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
